--- a/one2fan.com_g2_USD_CCUSD_20260701__20260731_country.xlsx
+++ b/one2fan.com_g2_USD_CCUSD_20260701__20260731_country.xlsx
@@ -562,7 +562,7 @@
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="K20" s="1" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="K22" s="1" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="K23" s="1" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="K24" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="K25" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="K27" s="1" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="K28" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="K29" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="K30" s="1" t="inlineStr">
         <is>
-          <t>Cayman Islands</t>
+          <t>KY</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="K31" s="1" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="K32" s="1" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="K33" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="K34" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="K35" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="K36" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="K37" s="1" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="K38" s="1" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K39" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="K40" s="1" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="K41" s="1" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="K42" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="K43" s="1" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="K44" s="1" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="K45" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="K46" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="K47" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="K48" s="1" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="K49" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="K50" s="1" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="K51" s="1" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="K52" s="1" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="K53" s="1" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="K54" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="K55" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="K56" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="K57" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="K58" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="K59" s="1" t="inlineStr">
         <is>
-          <t>Cayman Islands</t>
+          <t>KY</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="K60" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="K61" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="K62" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="K63" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="K64" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K65" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="K66" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="K67" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="K68" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="K69" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="K70" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="K71" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="K72" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="K73" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="K74" s="1" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="K75" s="1" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="K76" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="K77" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="K78" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="K79" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="K80" s="1" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="K81" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="K82" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="K83" s="1" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="K84" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="K85" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="K86" s="1" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="K87" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="K88" s="1" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="K89" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="K90" s="1" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="K91" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="K92" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="K93" s="1" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="K94" s="1" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="K95" s="1" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="K96" s="1" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="K97" s="1" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="K98" s="1" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="K99" s="1" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="K100" s="1" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="K101" s="1" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="K102" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="K103" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="K104" s="1" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="K105" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="K106" s="1" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="K107" s="1" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="K108" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -6490,7 +6490,7 @@
       </c>
       <c r="K109" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="K110" s="1" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="K111" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="K112" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="K113" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K114" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="K115" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="K116" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="K117" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="K118" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="K119" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="K120" s="1" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="K121" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="K122" s="1" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="K123" s="1" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="K124" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="K125" s="1" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="K126" s="1" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="K127" s="1" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="K128" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="K129" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="K130" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="K131" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="K132" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="K133" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="K134" s="1" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -7972,7 +7972,7 @@
       </c>
       <c r="K135" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8029,7 +8029,7 @@
       </c>
       <c r="K136" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="K137" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -8143,7 +8143,7 @@
       </c>
       <c r="K138" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="K139" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -8257,7 +8257,7 @@
       </c>
       <c r="K140" s="1" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="K141" s="1" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="K142" s="1" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="K143" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="K144" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="K145" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="K146" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="K147" s="1" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="K148" s="1" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="K149" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="K150" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="K151" s="1" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="K152" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="K153" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="K154" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="K155" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="K156" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="K157" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -9283,7 +9283,7 @@
       </c>
       <c r="K158" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="K159" s="1" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="K160" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="K161" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="K162" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K163" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -9625,7 +9625,7 @@
       </c>
       <c r="K164" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="K165" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="K166" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="K167" s="1" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="K168" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -9910,7 +9910,7 @@
       </c>
       <c r="K169" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="K170" s="1" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="K171" s="1" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -10081,7 +10081,7 @@
       </c>
       <c r="K172" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="K173" s="1" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>GH</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="K174" s="1" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="K175" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="K176" s="1" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="K177" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="K178" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -10480,7 +10480,7 @@
       </c>
       <c r="K179" s="1" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="K180" s="1" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="K181" s="1" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="K182" s="1" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="K183" s="1" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="K184" s="1" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -10822,7 +10822,7 @@
       </c>
       <c r="K185" s="1" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -10879,7 +10879,7 @@
       </c>
       <c r="K186" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="K187" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -10993,7 +10993,7 @@
       </c>
       <c r="K188" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -11050,7 +11050,7 @@
       </c>
       <c r="K189" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="K190" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -11164,7 +11164,7 @@
       </c>
       <c r="K191" s="1" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -11221,7 +11221,7 @@
       </c>
       <c r="K192" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -11278,7 +11278,7 @@
       </c>
       <c r="K193" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -11335,7 +11335,7 @@
       </c>
       <c r="K194" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="K195" s="1" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -11449,7 +11449,7 @@
       </c>
       <c r="K196" s="1" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="K197" s="1" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -11563,7 +11563,7 @@
       </c>
       <c r="K198" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="K199" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="K200" s="1" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="K201" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -11791,7 +11791,7 @@
       </c>
       <c r="K202" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="K203" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="K204" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="K205" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="K206" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="K207" s="1" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -12133,7 +12133,7 @@
       </c>
       <c r="K208" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="K209" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -12247,7 +12247,7 @@
       </c>
       <c r="K210" s="1" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -12304,7 +12304,7 @@
       </c>
       <c r="K211" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -12361,7 +12361,7 @@
       </c>
       <c r="K212" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -12418,7 +12418,7 @@
       </c>
       <c r="K213" s="1" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="K214" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -12532,7 +12532,7 @@
       </c>
       <c r="K215" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -12589,7 +12589,7 @@
       </c>
       <c r="K216" s="1" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -12646,7 +12646,7 @@
       </c>
       <c r="K217" s="1" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -12703,7 +12703,7 @@
       </c>
       <c r="K218" s="1" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -12760,7 +12760,7 @@
       </c>
       <c r="K219" s="1" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="K220" s="1" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -12874,7 +12874,7 @@
       </c>
       <c r="K221" s="1" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="K222" s="1" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="K223" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -13045,7 +13045,7 @@
       </c>
       <c r="K224" s="1" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -13102,7 +13102,7 @@
       </c>
       <c r="K225" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -13159,7 +13159,7 @@
       </c>
       <c r="K226" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="K227" s="1" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -13273,7 +13273,7 @@
       </c>
       <c r="K228" s="1" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -13330,7 +13330,7 @@
       </c>
       <c r="K229" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -13387,7 +13387,7 @@
       </c>
       <c r="K230" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="K231" s="1" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -13501,7 +13501,7 @@
       </c>
       <c r="K232" s="1" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="K233" s="1" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -13615,7 +13615,7 @@
       </c>
       <c r="K234" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="K235" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -13729,7 +13729,7 @@
       </c>
       <c r="K236" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="K237" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="K238" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -13900,7 +13900,7 @@
       </c>
       <c r="K239" s="1" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -13957,7 +13957,7 @@
       </c>
       <c r="K240" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="K241" s="1" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -14071,7 +14071,7 @@
       </c>
       <c r="K242" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -14128,7 +14128,7 @@
       </c>
       <c r="K243" s="1" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -14185,7 +14185,7 @@
       </c>
       <c r="K244" s="1" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="K245" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -14299,7 +14299,7 @@
       </c>
       <c r="K246" s="1" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -14356,7 +14356,7 @@
       </c>
       <c r="K247" s="1" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="K248" s="1" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="K249" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="K250" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="K251" s="1" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -14641,7 +14641,7 @@
       </c>
       <c r="K252" s="1" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -14698,7 +14698,7 @@
       </c>
       <c r="K253" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="K254" s="1" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -14812,7 +14812,7 @@
       </c>
       <c r="K255" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -14869,7 +14869,7 @@
       </c>
       <c r="K256" s="1" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -14926,7 +14926,7 @@
       </c>
       <c r="K257" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -14983,7 +14983,7 @@
       </c>
       <c r="K258" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -15040,7 +15040,7 @@
       </c>
       <c r="K259" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -15097,7 +15097,7 @@
       </c>
       <c r="K260" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -15154,7 +15154,7 @@
       </c>
       <c r="K261" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -15211,7 +15211,7 @@
       </c>
       <c r="K262" s="1" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -15268,7 +15268,7 @@
       </c>
       <c r="K263" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -15325,7 +15325,7 @@
       </c>
       <c r="K264" s="1" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="K265" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -15439,7 +15439,7 @@
       </c>
       <c r="K266" s="1" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -15496,7 +15496,7 @@
       </c>
       <c r="K267" s="1" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -15553,7 +15553,7 @@
       </c>
       <c r="K268" s="1" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -15610,7 +15610,7 @@
       </c>
       <c r="K269" s="1" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="K270" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -15724,7 +15724,7 @@
       </c>
       <c r="K271" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -15781,7 +15781,7 @@
       </c>
       <c r="K272" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -15838,7 +15838,7 @@
       </c>
       <c r="K273" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -15895,7 +15895,7 @@
       </c>
       <c r="K274" s="1" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="K275" s="1" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -16009,7 +16009,7 @@
       </c>
       <c r="K276" s="1" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="K277" s="1" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -16123,7 +16123,7 @@
       </c>
       <c r="K278" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -16180,7 +16180,7 @@
       </c>
       <c r="K279" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -16237,7 +16237,7 @@
       </c>
       <c r="K280" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -16294,7 +16294,7 @@
       </c>
       <c r="K281" s="1" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -16351,7 +16351,7 @@
       </c>
       <c r="K282" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -16408,7 +16408,7 @@
       </c>
       <c r="K283" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -16465,7 +16465,7 @@
       </c>
       <c r="K284" s="1" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -16522,7 +16522,7 @@
       </c>
       <c r="K285" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -16579,7 +16579,7 @@
       </c>
       <c r="K286" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -16636,7 +16636,7 @@
       </c>
       <c r="K287" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -16693,7 +16693,7 @@
       </c>
       <c r="K288" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -16750,7 +16750,7 @@
       </c>
       <c r="K289" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="K290" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -16864,7 +16864,7 @@
       </c>
       <c r="K291" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -16921,7 +16921,7 @@
       </c>
       <c r="K292" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -16978,7 +16978,7 @@
       </c>
       <c r="K293" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -17035,7 +17035,7 @@
       </c>
       <c r="K294" s="1" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>GH</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
@@ -17092,7 +17092,7 @@
       </c>
       <c r="K295" s="1" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -17149,7 +17149,7 @@
       </c>
       <c r="K296" s="1" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="K297" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
@@ -17263,7 +17263,7 @@
       </c>
       <c r="K298" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -17320,7 +17320,7 @@
       </c>
       <c r="K299" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
@@ -17377,7 +17377,7 @@
       </c>
       <c r="K300" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -17434,7 +17434,7 @@
       </c>
       <c r="K301" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="K302" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
@@ -17548,7 +17548,7 @@
       </c>
       <c r="K303" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -17605,7 +17605,7 @@
       </c>
       <c r="K304" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
@@ -17662,7 +17662,7 @@
       </c>
       <c r="K305" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -17719,7 +17719,7 @@
       </c>
       <c r="K306" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -17776,7 +17776,7 @@
       </c>
       <c r="K307" s="1" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -17833,7 +17833,7 @@
       </c>
       <c r="K308" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
@@ -17890,7 +17890,7 @@
       </c>
       <c r="K309" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
@@ -17947,7 +17947,7 @@
       </c>
       <c r="K310" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="K311" s="1" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
@@ -18061,7 +18061,7 @@
       </c>
       <c r="K312" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
@@ -18118,7 +18118,7 @@
       </c>
       <c r="K313" s="1" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
@@ -18175,7 +18175,7 @@
       </c>
       <c r="K314" s="1" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
@@ -18232,7 +18232,7 @@
       </c>
       <c r="K315" s="1" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
@@ -18289,7 +18289,7 @@
       </c>
       <c r="K316" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
@@ -18346,7 +18346,7 @@
       </c>
       <c r="K317" s="1" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -18403,7 +18403,7 @@
       </c>
       <c r="K318" s="1" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -18460,7 +18460,7 @@
       </c>
       <c r="K319" s="1" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
@@ -18517,7 +18517,7 @@
       </c>
       <c r="K320" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -18574,7 +18574,7 @@
       </c>
       <c r="K321" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -18631,7 +18631,7 @@
       </c>
       <c r="K322" s="1" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -18688,7 +18688,7 @@
       </c>
       <c r="K323" s="1" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -18745,7 +18745,7 @@
       </c>
       <c r="K324" s="1" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
@@ -18802,7 +18802,7 @@
       </c>
       <c r="K325" s="1" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
@@ -18859,7 +18859,7 @@
       </c>
       <c r="K326" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -18916,7 +18916,7 @@
       </c>
       <c r="K327" s="1" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -18973,7 +18973,7 @@
       </c>
       <c r="K328" s="1" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -19030,7 +19030,7 @@
       </c>
       <c r="K329" s="1" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
@@ -19087,7 +19087,7 @@
       </c>
       <c r="K330" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -19144,7 +19144,7 @@
       </c>
       <c r="K331" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -19201,7 +19201,7 @@
       </c>
       <c r="K332" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
@@ -19258,7 +19258,7 @@
       </c>
       <c r="K333" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
@@ -19315,7 +19315,7 @@
       </c>
       <c r="K334" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
@@ -19372,7 +19372,7 @@
       </c>
       <c r="K335" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
@@ -19429,7 +19429,7 @@
       </c>
       <c r="K336" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
@@ -19486,7 +19486,7 @@
       </c>
       <c r="K337" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
@@ -19543,7 +19543,7 @@
       </c>
       <c r="K338" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
@@ -19600,7 +19600,7 @@
       </c>
       <c r="K339" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
@@ -19657,7 +19657,7 @@
       </c>
       <c r="K340" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
@@ -19714,7 +19714,7 @@
       </c>
       <c r="K341" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
@@ -19771,7 +19771,7 @@
       </c>
       <c r="K342" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
@@ -19828,7 +19828,7 @@
       </c>
       <c r="K343" s="1" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
@@ -19885,7 +19885,7 @@
       </c>
       <c r="K344" s="1" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
@@ -19942,7 +19942,7 @@
       </c>
       <c r="K345" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
@@ -19999,7 +19999,7 @@
       </c>
       <c r="K346" s="1" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
@@ -20056,7 +20056,7 @@
       </c>
       <c r="K347" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
@@ -20113,7 +20113,7 @@
       </c>
       <c r="K348" s="1" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
@@ -20170,7 +20170,7 @@
       </c>
       <c r="K349" s="1" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>KH</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
@@ -20227,7 +20227,7 @@
       </c>
       <c r="K350" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
@@ -20284,7 +20284,7 @@
       </c>
       <c r="K351" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
@@ -20341,7 +20341,7 @@
       </c>
       <c r="K352" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
@@ -20398,7 +20398,7 @@
       </c>
       <c r="K353" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
@@ -20455,7 +20455,7 @@
       </c>
       <c r="K354" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
@@ -20512,7 +20512,7 @@
       </c>
       <c r="K355" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
@@ -20569,7 +20569,7 @@
       </c>
       <c r="K356" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
@@ -20626,7 +20626,7 @@
       </c>
       <c r="K357" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
@@ -20683,7 +20683,7 @@
       </c>
       <c r="K358" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="K359" s="1" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
@@ -20797,7 +20797,7 @@
       </c>
       <c r="K360" s="1" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
@@ -20854,7 +20854,7 @@
       </c>
       <c r="K361" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
@@ -20911,7 +20911,7 @@
       </c>
       <c r="K362" s="1" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="K363" s="1" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
@@ -21025,7 +21025,7 @@
       </c>
       <c r="K364" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
@@ -21082,7 +21082,7 @@
       </c>
       <c r="K365" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
@@ -21139,7 +21139,7 @@
       </c>
       <c r="K366" s="1" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
@@ -21196,7 +21196,7 @@
       </c>
       <c r="K367" s="1" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
@@ -21253,7 +21253,7 @@
       </c>
       <c r="K368" s="1" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
@@ -21310,7 +21310,7 @@
       </c>
       <c r="K369" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
@@ -21367,7 +21367,7 @@
       </c>
       <c r="K370" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
@@ -21424,7 +21424,7 @@
       </c>
       <c r="K371" s="1" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
@@ -21481,7 +21481,7 @@
       </c>
       <c r="K372" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
@@ -21538,7 +21538,7 @@
       </c>
       <c r="K373" s="1" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
@@ -21595,7 +21595,7 @@
       </c>
       <c r="K374" s="1" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
@@ -21652,7 +21652,7 @@
       </c>
       <c r="K375" s="1" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
@@ -21709,7 +21709,7 @@
       </c>
       <c r="K376" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
@@ -21766,7 +21766,7 @@
       </c>
       <c r="K377" s="1" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
@@ -21823,7 +21823,7 @@
       </c>
       <c r="K378" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
@@ -21880,7 +21880,7 @@
       </c>
       <c r="K379" s="1" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
@@ -21937,7 +21937,7 @@
       </c>
       <c r="K380" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="K381" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
@@ -22051,7 +22051,7 @@
       </c>
       <c r="K382" s="1" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
@@ -22108,7 +22108,7 @@
       </c>
       <c r="K383" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
@@ -22165,7 +22165,7 @@
       </c>
       <c r="K384" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
@@ -22222,7 +22222,7 @@
       </c>
       <c r="K385" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
@@ -22279,7 +22279,7 @@
       </c>
       <c r="K386" s="1" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
@@ -22336,7 +22336,7 @@
       </c>
       <c r="K387" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
@@ -22393,7 +22393,7 @@
       </c>
       <c r="K388" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
@@ -22450,7 +22450,7 @@
       </c>
       <c r="K389" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
@@ -22507,7 +22507,7 @@
       </c>
       <c r="K390" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
@@ -22564,7 +22564,7 @@
       </c>
       <c r="K391" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
@@ -22621,7 +22621,7 @@
       </c>
       <c r="K392" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
@@ -22678,7 +22678,7 @@
       </c>
       <c r="K393" s="1" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
@@ -22735,7 +22735,7 @@
       </c>
       <c r="K394" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
@@ -22792,7 +22792,7 @@
       </c>
       <c r="K395" s="1" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
@@ -22849,7 +22849,7 @@
       </c>
       <c r="K396" s="1" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
@@ -22906,7 +22906,7 @@
       </c>
       <c r="K397" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
@@ -22963,7 +22963,7 @@
       </c>
       <c r="K398" s="1" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
@@ -23020,7 +23020,7 @@
       </c>
       <c r="K399" s="1" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="L399" t="inlineStr">
@@ -23077,7 +23077,7 @@
       </c>
       <c r="K400" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="L400" t="inlineStr">
@@ -23134,7 +23134,7 @@
       </c>
       <c r="K401" s="1" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
@@ -23191,7 +23191,7 @@
       </c>
       <c r="K402" s="1" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
@@ -23248,7 +23248,7 @@
       </c>
       <c r="K403" s="1" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
@@ -23305,7 +23305,7 @@
       </c>
       <c r="K404" s="1" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
@@ -23362,7 +23362,7 @@
       </c>
       <c r="K405" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
@@ -23419,7 +23419,7 @@
       </c>
       <c r="K406" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
@@ -23476,7 +23476,7 @@
       </c>
       <c r="K407" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
@@ -23533,7 +23533,7 @@
       </c>
       <c r="K408" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
@@ -23590,7 +23590,7 @@
       </c>
       <c r="K409" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L409" t="inlineStr">
@@ -23647,7 +23647,7 @@
       </c>
       <c r="K410" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
@@ -23704,7 +23704,7 @@
       </c>
       <c r="K411" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
@@ -23761,7 +23761,7 @@
       </c>
       <c r="K412" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
@@ -23818,7 +23818,7 @@
       </c>
       <c r="K413" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="L413" t="inlineStr">
@@ -23875,7 +23875,7 @@
       </c>
       <c r="K414" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
@@ -23932,7 +23932,7 @@
       </c>
       <c r="K415" s="1" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="L415" t="inlineStr">
@@ -23989,7 +23989,7 @@
       </c>
       <c r="K416" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L416" t="inlineStr">
@@ -24046,7 +24046,7 @@
       </c>
       <c r="K417" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
@@ -24103,7 +24103,7 @@
       </c>
       <c r="K418" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L418" t="inlineStr">
@@ -24160,7 +24160,7 @@
       </c>
       <c r="K419" s="1" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
@@ -24217,7 +24217,7 @@
       </c>
       <c r="K420" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L420" t="inlineStr">
@@ -24274,7 +24274,7 @@
       </c>
       <c r="K421" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L421" t="inlineStr">
@@ -24331,7 +24331,7 @@
       </c>
       <c r="K422" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L422" t="inlineStr">
@@ -24388,7 +24388,7 @@
       </c>
       <c r="K423" s="1" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="L423" t="inlineStr">
@@ -24445,7 +24445,7 @@
       </c>
       <c r="K424" s="1" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="L424" t="inlineStr">
@@ -24502,7 +24502,7 @@
       </c>
       <c r="K425" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L425" t="inlineStr">
@@ -24559,7 +24559,7 @@
       </c>
       <c r="K426" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L426" t="inlineStr">
@@ -24616,7 +24616,7 @@
       </c>
       <c r="K427" s="1" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
@@ -24673,7 +24673,7 @@
       </c>
       <c r="K428" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
@@ -24730,7 +24730,7 @@
       </c>
       <c r="K429" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="K430" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
@@ -24844,7 +24844,7 @@
       </c>
       <c r="K431" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
@@ -24901,7 +24901,7 @@
       </c>
       <c r="K432" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
@@ -24958,7 +24958,7 @@
       </c>
       <c r="K433" s="1" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
@@ -25015,7 +25015,7 @@
       </c>
       <c r="K434" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L434" t="inlineStr">
@@ -25072,7 +25072,7 @@
       </c>
       <c r="K435" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L435" t="inlineStr">
@@ -25129,7 +25129,7 @@
       </c>
       <c r="K436" s="1" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">
@@ -25186,7 +25186,7 @@
       </c>
       <c r="K437" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
@@ -25243,7 +25243,7 @@
       </c>
       <c r="K438" s="1" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="L438" t="inlineStr">
@@ -25300,7 +25300,7 @@
       </c>
       <c r="K439" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
@@ -25357,7 +25357,7 @@
       </c>
       <c r="K440" s="1" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
@@ -25414,7 +25414,7 @@
       </c>
       <c r="K441" s="1" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="L441" t="inlineStr">
@@ -25471,7 +25471,7 @@
       </c>
       <c r="K442" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
@@ -25528,7 +25528,7 @@
       </c>
       <c r="K443" s="1" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="L443" t="inlineStr">
@@ -25585,7 +25585,7 @@
       </c>
       <c r="K444" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L444" t="inlineStr">
@@ -25642,7 +25642,7 @@
       </c>
       <c r="K445" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L445" t="inlineStr">
@@ -25699,7 +25699,7 @@
       </c>
       <c r="K446" s="1" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
@@ -25756,7 +25756,7 @@
       </c>
       <c r="K447" s="1" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
@@ -25813,7 +25813,7 @@
       </c>
       <c r="K448" s="1" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="L448" t="inlineStr">
@@ -25870,7 +25870,7 @@
       </c>
       <c r="K449" s="1" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="L449" t="inlineStr">
@@ -25927,7 +25927,7 @@
       </c>
       <c r="K450" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L450" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="K451" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L451" t="inlineStr">
@@ -26041,7 +26041,7 @@
       </c>
       <c r="K452" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
@@ -26098,7 +26098,7 @@
       </c>
       <c r="K453" s="1" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
@@ -26155,7 +26155,7 @@
       </c>
       <c r="K454" s="1" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>KH</t>
         </is>
       </c>
       <c r="L454" t="inlineStr">
@@ -26212,7 +26212,7 @@
       </c>
       <c r="K455" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
@@ -26269,7 +26269,7 @@
       </c>
       <c r="K456" s="1" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
@@ -26326,7 +26326,7 @@
       </c>
       <c r="K457" s="1" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
@@ -26383,7 +26383,7 @@
       </c>
       <c r="K458" s="1" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
@@ -26440,7 +26440,7 @@
       </c>
       <c r="K459" s="1" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
@@ -26497,7 +26497,7 @@
       </c>
       <c r="K460" s="1" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
@@ -26554,7 +26554,7 @@
       </c>
       <c r="K461" s="1" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
@@ -26611,7 +26611,7 @@
       </c>
       <c r="K462" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
@@ -26668,7 +26668,7 @@
       </c>
       <c r="K463" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L463" t="inlineStr">
@@ -26725,7 +26725,7 @@
       </c>
       <c r="K464" s="1" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
@@ -26782,7 +26782,7 @@
       </c>
       <c r="K465" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
@@ -26839,7 +26839,7 @@
       </c>
       <c r="K466" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
@@ -26896,7 +26896,7 @@
       </c>
       <c r="K467" s="1" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
@@ -26953,7 +26953,7 @@
       </c>
       <c r="K468" s="1" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
@@ -27010,7 +27010,7 @@
       </c>
       <c r="K469" s="1" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
@@ -27067,7 +27067,7 @@
       </c>
       <c r="K470" s="1" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
@@ -27124,7 +27124,7 @@
       </c>
       <c r="K471" s="1" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
@@ -27181,7 +27181,7 @@
       </c>
       <c r="K472" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
@@ -27238,7 +27238,7 @@
       </c>
       <c r="K473" s="1" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
@@ -27295,7 +27295,7 @@
       </c>
       <c r="K474" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
@@ -27352,7 +27352,7 @@
       </c>
       <c r="K475" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
@@ -27409,7 +27409,7 @@
       </c>
       <c r="K476" s="1" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
@@ -27466,7 +27466,7 @@
       </c>
       <c r="K477" s="1" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="L477" t="inlineStr">
@@ -27523,7 +27523,7 @@
       </c>
       <c r="K478" s="1" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="L478" t="inlineStr">
@@ -27580,7 +27580,7 @@
       </c>
       <c r="K479" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
@@ -27637,7 +27637,7 @@
       </c>
       <c r="K480" s="1" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
@@ -27694,7 +27694,7 @@
       </c>
       <c r="K481" s="1" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="L481" t="inlineStr">
@@ -27751,7 +27751,7 @@
       </c>
       <c r="K482" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
@@ -27808,7 +27808,7 @@
       </c>
       <c r="K483" s="1" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="L483" t="inlineStr">
@@ -27865,7 +27865,7 @@
       </c>
       <c r="K484" s="1" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="L484" t="inlineStr">
@@ -27922,7 +27922,7 @@
       </c>
       <c r="K485" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L485" t="inlineStr">
@@ -27979,7 +27979,7 @@
       </c>
       <c r="K486" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L486" t="inlineStr">
@@ -28036,7 +28036,7 @@
       </c>
       <c r="K487" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L487" t="inlineStr">
@@ -28093,7 +28093,7 @@
       </c>
       <c r="K488" s="1" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="L488" t="inlineStr">
@@ -28150,7 +28150,7 @@
       </c>
       <c r="K489" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L489" t="inlineStr">
@@ -28207,7 +28207,7 @@
       </c>
       <c r="K490" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L490" t="inlineStr">
@@ -28264,7 +28264,7 @@
       </c>
       <c r="K491" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L491" t="inlineStr">
@@ -28321,7 +28321,7 @@
       </c>
       <c r="K492" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L492" t="inlineStr">
@@ -28378,7 +28378,7 @@
       </c>
       <c r="K493" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L493" t="inlineStr">
@@ -28435,7 +28435,7 @@
       </c>
       <c r="K494" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L494" t="inlineStr">
@@ -28492,7 +28492,7 @@
       </c>
       <c r="K495" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L495" t="inlineStr">
@@ -28549,7 +28549,7 @@
       </c>
       <c r="K496" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
@@ -28606,7 +28606,7 @@
       </c>
       <c r="K497" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
@@ -28663,7 +28663,7 @@
       </c>
       <c r="K498" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L498" t="inlineStr">
@@ -28720,7 +28720,7 @@
       </c>
       <c r="K499" s="1" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="L499" t="inlineStr">
@@ -28777,7 +28777,7 @@
       </c>
       <c r="K500" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
@@ -28834,7 +28834,7 @@
       </c>
       <c r="K501" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
@@ -28891,7 +28891,7 @@
       </c>
       <c r="K502" s="1" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="L502" t="inlineStr">
@@ -28948,7 +28948,7 @@
       </c>
       <c r="K503" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L503" t="inlineStr">
@@ -29005,7 +29005,7 @@
       </c>
       <c r="K504" s="1" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="L504" t="inlineStr">
@@ -29062,7 +29062,7 @@
       </c>
       <c r="K505" s="1" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L505" t="inlineStr">
@@ -29119,7 +29119,7 @@
       </c>
       <c r="K506" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
@@ -29176,7 +29176,7 @@
       </c>
       <c r="K507" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
@@ -29233,7 +29233,7 @@
       </c>
       <c r="K508" s="1" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
@@ -29290,7 +29290,7 @@
       </c>
       <c r="K509" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L509" t="inlineStr">
@@ -29347,7 +29347,7 @@
       </c>
       <c r="K510" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L510" t="inlineStr">
@@ -29404,7 +29404,7 @@
       </c>
       <c r="K511" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L511" t="inlineStr">
@@ -29461,7 +29461,7 @@
       </c>
       <c r="K512" s="1" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="L512" t="inlineStr">
@@ -29518,7 +29518,7 @@
       </c>
       <c r="K513" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L513" t="inlineStr">
@@ -29575,7 +29575,7 @@
       </c>
       <c r="K514" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L514" t="inlineStr">
@@ -29632,7 +29632,7 @@
       </c>
       <c r="K515" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L515" t="inlineStr">
@@ -29689,7 +29689,7 @@
       </c>
       <c r="K516" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L516" t="inlineStr">
@@ -29746,7 +29746,7 @@
       </c>
       <c r="K517" s="1" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="L517" t="inlineStr">
@@ -29803,7 +29803,7 @@
       </c>
       <c r="K518" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="L518" t="inlineStr">
@@ -29860,7 +29860,7 @@
       </c>
       <c r="K519" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L519" t="inlineStr">
@@ -29917,7 +29917,7 @@
       </c>
       <c r="K520" s="1" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="K521" s="1" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
@@ -30031,7 +30031,7 @@
       </c>
       <c r="K522" s="1" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
@@ -30088,7 +30088,7 @@
       </c>
       <c r="K523" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L523" t="inlineStr">
@@ -30145,7 +30145,7 @@
       </c>
       <c r="K524" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L524" t="inlineStr">
@@ -30202,7 +30202,7 @@
       </c>
       <c r="K525" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="L525" t="inlineStr">
@@ -30259,7 +30259,7 @@
       </c>
       <c r="K526" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L526" t="inlineStr">
@@ -30316,7 +30316,7 @@
       </c>
       <c r="K527" s="1" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>UA</t>
         </is>
       </c>
       <c r="L527" t="inlineStr">
@@ -30373,7 +30373,7 @@
       </c>
       <c r="K528" s="1" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="L528" t="inlineStr">
@@ -30430,7 +30430,7 @@
       </c>
       <c r="K529" s="1" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="L529" t="inlineStr">
@@ -30487,7 +30487,7 @@
       </c>
       <c r="K530" s="1" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="L530" t="inlineStr">
@@ -30544,7 +30544,7 @@
       </c>
       <c r="K531" s="1" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="L531" t="inlineStr">
@@ -30601,7 +30601,7 @@
       </c>
       <c r="K532" s="1" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="L532" t="inlineStr">
@@ -30658,7 +30658,7 @@
       </c>
       <c r="K533" s="1" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="L533" t="inlineStr">
@@ -30715,7 +30715,7 @@
       </c>
       <c r="K534" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L534" t="inlineStr">
@@ -30772,7 +30772,7 @@
       </c>
       <c r="K535" s="1" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="L535" t="inlineStr">
@@ -30829,7 +30829,7 @@
       </c>
       <c r="K536" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L536" t="inlineStr">
@@ -30886,7 +30886,7 @@
       </c>
       <c r="K537" s="1" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="L537" t="inlineStr">
@@ -30943,7 +30943,7 @@
       </c>
       <c r="K538" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L538" t="inlineStr">
@@ -31000,7 +31000,7 @@
       </c>
       <c r="K539" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L539" t="inlineStr">
@@ -31057,7 +31057,7 @@
       </c>
       <c r="K540" s="1" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="L540" t="inlineStr">
@@ -31114,7 +31114,7 @@
       </c>
       <c r="K541" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L541" t="inlineStr">
@@ -31171,7 +31171,7 @@
       </c>
       <c r="K542" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L542" t="inlineStr">
@@ -31228,7 +31228,7 @@
       </c>
       <c r="K543" s="1" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="L543" t="inlineStr">
@@ -31285,7 +31285,7 @@
       </c>
       <c r="K544" s="1" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="L544" t="inlineStr">
@@ -31342,7 +31342,7 @@
       </c>
       <c r="K545" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="L545" t="inlineStr">
@@ -31399,7 +31399,7 @@
       </c>
       <c r="K546" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L546" t="inlineStr">
@@ -31456,7 +31456,7 @@
       </c>
       <c r="K547" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L547" t="inlineStr">
@@ -31513,7 +31513,7 @@
       </c>
       <c r="K548" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L548" t="inlineStr">
@@ -31570,7 +31570,7 @@
       </c>
       <c r="K549" s="1" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="L549" t="inlineStr">
@@ -31627,7 +31627,7 @@
       </c>
       <c r="K550" s="1" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="L550" t="inlineStr">
@@ -31684,7 +31684,7 @@
       </c>
       <c r="K551" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L551" t="inlineStr">
@@ -31741,7 +31741,7 @@
       </c>
       <c r="K552" s="1" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="L552" t="inlineStr">
@@ -31798,7 +31798,7 @@
       </c>
       <c r="K553" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L553" t="inlineStr">
@@ -31855,7 +31855,7 @@
       </c>
       <c r="K554" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L554" t="inlineStr">
@@ -31912,7 +31912,7 @@
       </c>
       <c r="K555" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L555" t="inlineStr">
@@ -31969,7 +31969,7 @@
       </c>
       <c r="K556" s="1" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="L556" t="inlineStr">
@@ -32026,7 +32026,7 @@
       </c>
       <c r="K557" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L557" t="inlineStr">
@@ -32083,7 +32083,7 @@
       </c>
       <c r="K558" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L558" t="inlineStr">
@@ -32140,7 +32140,7 @@
       </c>
       <c r="K559" s="1" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="L559" t="inlineStr">
@@ -32197,7 +32197,7 @@
       </c>
       <c r="K560" s="1" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="L560" t="inlineStr">
@@ -32254,7 +32254,7 @@
       </c>
       <c r="K561" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L561" t="inlineStr">
@@ -32311,7 +32311,7 @@
       </c>
       <c r="K562" s="1" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="L562" t="inlineStr">
@@ -32368,7 +32368,7 @@
       </c>
       <c r="K563" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L563" t="inlineStr">
@@ -32425,7 +32425,7 @@
       </c>
       <c r="K564" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="L564" t="inlineStr">
@@ -32482,7 +32482,7 @@
       </c>
       <c r="K565" s="1" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="L565" t="inlineStr">
@@ -32539,7 +32539,7 @@
       </c>
       <c r="K566" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L566" t="inlineStr">
@@ -32596,7 +32596,7 @@
       </c>
       <c r="K567" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="L567" t="inlineStr">
@@ -32653,7 +32653,7 @@
       </c>
       <c r="K568" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L568" t="inlineStr">
@@ -32710,7 +32710,7 @@
       </c>
       <c r="K569" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L569" t="inlineStr">
@@ -32767,7 +32767,7 @@
       </c>
       <c r="K570" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L570" t="inlineStr">
@@ -32824,7 +32824,7 @@
       </c>
       <c r="K571" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L571" t="inlineStr">
@@ -32881,7 +32881,7 @@
       </c>
       <c r="K572" s="1" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="L572" t="inlineStr">
@@ -32938,7 +32938,7 @@
       </c>
       <c r="K573" s="1" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="L573" t="inlineStr">
@@ -32995,7 +32995,7 @@
       </c>
       <c r="K574" s="1" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="L574" t="inlineStr">
@@ -33052,7 +33052,7 @@
       </c>
       <c r="K575" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L575" t="inlineStr">
@@ -33109,7 +33109,7 @@
       </c>
       <c r="K576" s="1" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="L576" t="inlineStr">
@@ -33166,7 +33166,7 @@
       </c>
       <c r="K577" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L577" t="inlineStr">
@@ -33223,7 +33223,7 @@
       </c>
       <c r="K578" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L578" t="inlineStr">
@@ -33280,7 +33280,7 @@
       </c>
       <c r="K579" s="1" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="L579" t="inlineStr">
@@ -33337,7 +33337,7 @@
       </c>
       <c r="K580" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L580" t="inlineStr">
@@ -33394,7 +33394,7 @@
       </c>
       <c r="K581" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L581" t="inlineStr">
@@ -33451,7 +33451,7 @@
       </c>
       <c r="K582" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L582" t="inlineStr">
@@ -33508,7 +33508,7 @@
       </c>
       <c r="K583" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L583" t="inlineStr">
@@ -33565,7 +33565,7 @@
       </c>
       <c r="K584" s="1" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="L584" t="inlineStr">
@@ -33622,7 +33622,7 @@
       </c>
       <c r="K585" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L585" t="inlineStr">
@@ -33679,7 +33679,7 @@
       </c>
       <c r="K586" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L586" t="inlineStr">
@@ -33736,7 +33736,7 @@
       </c>
       <c r="K587" s="1" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="L587" t="inlineStr">
@@ -33793,7 +33793,7 @@
       </c>
       <c r="K588" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L588" t="inlineStr">
@@ -33850,7 +33850,7 @@
       </c>
       <c r="K589" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L589" t="inlineStr">
@@ -33907,7 +33907,7 @@
       </c>
       <c r="K590" s="1" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="L590" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="K591" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L591" t="inlineStr">
@@ -34021,7 +34021,7 @@
       </c>
       <c r="K592" s="1" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="L592" t="inlineStr">
@@ -34078,7 +34078,7 @@
       </c>
       <c r="K593" s="1" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="L593" t="inlineStr">
@@ -34135,7 +34135,7 @@
       </c>
       <c r="K594" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L594" t="inlineStr">
@@ -34192,7 +34192,7 @@
       </c>
       <c r="K595" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L595" t="inlineStr">
@@ -34249,7 +34249,7 @@
       </c>
       <c r="K596" s="1" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="L596" t="inlineStr">
@@ -34306,7 +34306,7 @@
       </c>
       <c r="K597" s="1" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="L597" t="inlineStr">
@@ -34363,7 +34363,7 @@
       </c>
       <c r="K598" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L598" t="inlineStr">
@@ -34420,7 +34420,7 @@
       </c>
       <c r="K599" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L599" t="inlineStr">
@@ -34477,7 +34477,7 @@
       </c>
       <c r="K600" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L600" t="inlineStr">
@@ -34534,7 +34534,7 @@
       </c>
       <c r="K601" s="1" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="L601" t="inlineStr">
@@ -34591,7 +34591,7 @@
       </c>
       <c r="K602" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L602" t="inlineStr">
@@ -34648,7 +34648,7 @@
       </c>
       <c r="K603" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L603" t="inlineStr">
@@ -34705,7 +34705,7 @@
       </c>
       <c r="K604" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L604" t="inlineStr">
@@ -34762,7 +34762,7 @@
       </c>
       <c r="K605" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L605" t="inlineStr">
@@ -34819,7 +34819,7 @@
       </c>
       <c r="K606" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L606" t="inlineStr">
@@ -34876,7 +34876,7 @@
       </c>
       <c r="K607" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L607" t="inlineStr">
@@ -34933,7 +34933,7 @@
       </c>
       <c r="K608" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L608" t="inlineStr">
@@ -34990,7 +34990,7 @@
       </c>
       <c r="K609" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L609" t="inlineStr">
@@ -35047,7 +35047,7 @@
       </c>
       <c r="K610" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L610" t="inlineStr">
@@ -35104,7 +35104,7 @@
       </c>
       <c r="K611" s="1" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="L611" t="inlineStr">
@@ -35161,7 +35161,7 @@
       </c>
       <c r="K612" s="1" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="L612" t="inlineStr">
@@ -35218,7 +35218,7 @@
       </c>
       <c r="K613" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L613" t="inlineStr">
@@ -35275,7 +35275,7 @@
       </c>
       <c r="K614" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L614" t="inlineStr">
@@ -35332,7 +35332,7 @@
       </c>
       <c r="K615" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L615" t="inlineStr">
@@ -35389,7 +35389,7 @@
       </c>
       <c r="K616" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="L616" t="inlineStr">
@@ -35446,7 +35446,7 @@
       </c>
       <c r="K617" s="1" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L617" t="inlineStr">
@@ -35503,7 +35503,7 @@
       </c>
       <c r="K618" s="1" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="L618" t="inlineStr">
@@ -35560,7 +35560,7 @@
       </c>
       <c r="K619" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="L619" t="inlineStr">
@@ -35617,7 +35617,7 @@
       </c>
       <c r="K620" s="1" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="L620" t="inlineStr">
@@ -35674,7 +35674,7 @@
       </c>
       <c r="K621" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L621" t="inlineStr">
@@ -35731,7 +35731,7 @@
       </c>
       <c r="K622" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L622" t="inlineStr">
@@ -35788,7 +35788,7 @@
       </c>
       <c r="K623" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L623" t="inlineStr">
@@ -35845,7 +35845,7 @@
       </c>
       <c r="K624" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L624" t="inlineStr">
@@ -35902,7 +35902,7 @@
       </c>
       <c r="K625" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="L625" t="inlineStr">
@@ -35959,7 +35959,7 @@
       </c>
       <c r="K626" s="1" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L626" t="inlineStr">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="K627" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L627" t="inlineStr">
@@ -36073,7 +36073,7 @@
       </c>
       <c r="K628" s="1" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="L628" t="inlineStr">
@@ -36130,7 +36130,7 @@
       </c>
       <c r="K629" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="L629" t="inlineStr">
@@ -36187,7 +36187,7 @@
       </c>
       <c r="K630" s="1" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="L630" t="inlineStr">
@@ -36244,7 +36244,7 @@
       </c>
       <c r="K631" s="1" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="L631" t="inlineStr">
@@ -36301,7 +36301,7 @@
       </c>
       <c r="K632" s="1" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="L632" t="inlineStr">
@@ -36358,7 +36358,7 @@
       </c>
       <c r="K633" s="1" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="L633" t="inlineStr">
@@ -36415,7 +36415,7 @@
       </c>
       <c r="K634" s="1" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="L634" t="inlineStr">
@@ -36472,7 +36472,7 @@
       </c>
       <c r="K635" s="1" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L635" t="inlineStr">
@@ -36529,7 +36529,7 @@
       </c>
       <c r="K636" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L636" t="inlineStr">
@@ -36586,7 +36586,7 @@
       </c>
       <c r="K637" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L637" t="inlineStr">
@@ -36643,7 +36643,7 @@
       </c>
       <c r="K638" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L638" t="inlineStr">
@@ -36700,7 +36700,7 @@
       </c>
       <c r="K639" s="1" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L639" t="inlineStr">
@@ -36757,7 +36757,7 @@
       </c>
       <c r="K640" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L640" t="inlineStr">
@@ -36814,7 +36814,7 @@
       </c>
       <c r="K641" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L641" t="inlineStr">
@@ -36871,7 +36871,7 @@
       </c>
       <c r="K642" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L642" t="inlineStr">
@@ -36928,7 +36928,7 @@
       </c>
       <c r="K643" s="1" t="inlineStr">
         <is>
-          <t>Cayman Islands</t>
+          <t>KY</t>
         </is>
       </c>
       <c r="L643" t="inlineStr">
@@ -36985,7 +36985,7 @@
       </c>
       <c r="K644" s="1" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="L644" t="inlineStr">
@@ -37042,7 +37042,7 @@
       </c>
       <c r="K645" s="1" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="L645" t="inlineStr">
@@ -37099,7 +37099,7 @@
       </c>
       <c r="K646" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L646" t="inlineStr">
@@ -37156,7 +37156,7 @@
       </c>
       <c r="K647" s="1" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="L647" t="inlineStr">
@@ -37213,7 +37213,7 @@
       </c>
       <c r="K648" s="1" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="L648" t="inlineStr">
@@ -37270,7 +37270,7 @@
       </c>
       <c r="K649" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L649" t="inlineStr">
@@ -37327,7 +37327,7 @@
       </c>
       <c r="K650" s="1" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="L650" t="inlineStr">
@@ -37384,7 +37384,7 @@
       </c>
       <c r="K651" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L651" t="inlineStr">
@@ -37441,7 +37441,7 @@
       </c>
       <c r="K652" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="L652" t="inlineStr">
@@ -37498,7 +37498,7 @@
       </c>
       <c r="K653" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L653" t="inlineStr">
@@ -37555,7 +37555,7 @@
       </c>
       <c r="K654" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L654" t="inlineStr">
@@ -37612,7 +37612,7 @@
       </c>
       <c r="K655" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L655" t="inlineStr">
@@ -37669,7 +37669,7 @@
       </c>
       <c r="K656" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L656" t="inlineStr">
@@ -37726,7 +37726,7 @@
       </c>
       <c r="K657" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="L657" t="inlineStr">
@@ -37783,7 +37783,7 @@
       </c>
       <c r="K658" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L658" t="inlineStr">
@@ -37840,7 +37840,7 @@
       </c>
       <c r="K659" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L659" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="K660" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L660" t="inlineStr">
@@ -37954,7 +37954,7 @@
       </c>
       <c r="K661" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="L661" t="inlineStr">
@@ -38011,7 +38011,7 @@
       </c>
       <c r="K662" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="L662" t="inlineStr">
@@ -38068,7 +38068,7 @@
       </c>
       <c r="K663" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="L663" t="inlineStr">
@@ -38125,7 +38125,7 @@
       </c>
       <c r="K664" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="L664" t="inlineStr">
